--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel4.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel4.xlsx
@@ -402,7 +402,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -588,6 +588,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -597,7 +600,7 @@
               <c:f>'model4(1)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -782,6 +785,9 @@
                   <c:v>9376392.18772012</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>9376392.18772012</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>9376392.18772012</c:v>
                 </c:pt>
               </c:numCache>
@@ -825,7 +831,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1011,6 +1017,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1020,7 +1029,7 @@
               <c:f>'model4(1)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1206,6 +1215,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>16585564.304557247</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>17355066.429656375</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1248,7 +1260,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1434,6 +1446,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1443,7 +1458,7 @@
               <c:f>'model4(1)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1629,6 +1644,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>7209172.1168371271</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>7978674.2419362552</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1650,11 +1668,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="94116096"/>
-        <c:axId val="99717504"/>
+        <c:axId val="492976000"/>
+        <c:axId val="492992768"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="94116096"/>
+        <c:axId val="492976000"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1697,14 +1715,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99717504"/>
+        <c:crossAx val="492992768"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="99717504"/>
+        <c:axId val="492992768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1755,7 +1773,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94116096"/>
+        <c:crossAx val="492976000"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1916,7 +1934,7 @@
               <c:f>'model4(1)'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2102,6 +2120,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-329147.77001413936</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-915628.10722505616</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2116,8 +2137,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="399839616"/>
-        <c:axId val="399528704"/>
+        <c:axId val="620200320"/>
+        <c:axId val="506750464"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2142,7 +2163,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -2328,6 +2349,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2337,7 +2361,7 @@
               <c:f>'model4(1)'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>4.7860299999999993</c:v>
                 </c:pt>
@@ -2523,6 +2547,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>5.970703125</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>6.2764160156250002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2539,11 +2566,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="161229824"/>
-        <c:axId val="390302336"/>
+        <c:axId val="500311552"/>
+        <c:axId val="500313088"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="161229824"/>
+        <c:axId val="500311552"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2586,14 +2613,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="390302336"/>
+        <c:crossAx val="500313088"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="390302336"/>
+        <c:axId val="500313088"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2644,12 +2671,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="161229824"/>
+        <c:crossAx val="500311552"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="399528704"/>
+        <c:axId val="506750464"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2686,12 +2713,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="399839616"/>
+        <c:crossAx val="620200320"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="399839616"/>
+        <c:axId val="620200320"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2700,7 +2727,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="399528704"/>
+        <c:crossAx val="506750464"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3109,7 +3136,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG64"/>
+  <dimension ref="A1:AG65"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -5813,6 +5840,44 @@
         <v>1556859.6476140034</v>
       </c>
     </row>
+    <row r="65" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A65" s="14">
+        <v>46203</v>
+      </c>
+      <c r="B65" s="15">
+        <v>6.2764160156250002</v>
+      </c>
+      <c r="C65" s="15">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D65" s="16">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E65" s="16">
+        <v>-915628.10722505616</v>
+      </c>
+      <c r="F65" s="17">
+        <v>-145883.90969394316</v>
+      </c>
+      <c r="G65" s="17">
+        <v>2371190.6026890925</v>
+      </c>
+      <c r="H65" s="17">
+        <v>14882578.674817316</v>
+      </c>
+      <c r="I65" s="17">
+        <v>9376392.18772012</v>
+      </c>
+      <c r="J65" s="17">
+        <v>17355066.429656375</v>
+      </c>
+      <c r="K65" s="17">
+        <v>7978674.2419362552</v>
+      </c>
+      <c r="L65" s="16">
+        <v>2472487.7548390594</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel4.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel4.xlsx
@@ -402,7 +402,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -591,6 +591,9 @@
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -600,7 +603,7 @@
               <c:f>'model4(1)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -788,6 +791,9 @@
                   <c:v>9376392.18772012</c:v>
                 </c:pt>
                 <c:pt idx="62">
+                  <c:v>9376392.18772012</c:v>
+                </c:pt>
+                <c:pt idx="63">
                   <c:v>9376392.18772012</c:v>
                 </c:pt>
               </c:numCache>
@@ -831,7 +837,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1020,6 +1026,9 @@
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1029,7 +1038,7 @@
               <c:f>'model4(1)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1218,6 +1227,9 @@
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>17355066.429656375</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>14891650.637779195</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1260,7 +1272,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1449,6 +1461,9 @@
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1458,7 +1473,7 @@
               <c:f>'model4(1)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1647,6 +1662,9 @@
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>7978674.2419362552</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>5515258.4500590749</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1668,11 +1686,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="492976000"/>
-        <c:axId val="492992768"/>
+        <c:axId val="77073408"/>
+        <c:axId val="508912384"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="492976000"/>
+        <c:axId val="77073408"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1715,14 +1733,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="492992768"/>
+        <c:crossAx val="508912384"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="492992768"/>
+        <c:axId val="508912384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1773,7 +1791,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="492976000"/>
+        <c:crossAx val="77073408"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1934,7 +1952,7 @@
               <c:f>'model4(1)'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2123,6 +2141,9 @@
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>-915628.10722505616</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>-314574.39222416701</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2137,8 +2158,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="620200320"/>
-        <c:axId val="506750464"/>
+        <c:axId val="676456704"/>
+        <c:axId val="676454784"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2163,7 +2184,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -2352,6 +2373,9 @@
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2361,7 +2385,7 @@
               <c:f>'model4(1)'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>4.7860299999999993</c:v>
                 </c:pt>
@@ -2550,6 +2574,9 @@
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>6.2764160156250002</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>5.2375219726562499</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2566,11 +2593,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="500311552"/>
-        <c:axId val="500313088"/>
+        <c:axId val="547349248"/>
+        <c:axId val="547351168"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="500311552"/>
+        <c:axId val="547349248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2613,14 +2640,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="500313088"/>
+        <c:crossAx val="547351168"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="500313088"/>
+        <c:axId val="547351168"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2671,12 +2698,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="500311552"/>
+        <c:crossAx val="547349248"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="506750464"/>
+        <c:axId val="676454784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2713,12 +2740,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="620200320"/>
+        <c:crossAx val="676456704"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="620200320"/>
+        <c:axId val="676456704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2727,7 +2754,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="506750464"/>
+        <c:crossAx val="676454784"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3136,7 +3163,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG65"/>
+  <dimension ref="A1:AG66"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -5878,6 +5905,44 @@
         <v>2472487.7548390594</v>
       </c>
     </row>
+    <row r="66" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A66" s="14">
+        <v>46234</v>
+      </c>
+      <c r="B66" s="15">
+        <v>5.2375219726562499</v>
+      </c>
+      <c r="C66" s="15">
+        <v>35.700000760000002</v>
+      </c>
+      <c r="D66" s="16">
+        <v>26.77592732691858</v>
+      </c>
+      <c r="E66" s="16">
+        <v>-314574.39222416701</v>
+      </c>
+      <c r="F66" s="17">
+        <v>-60061.684488672065</v>
+      </c>
+      <c r="G66" s="17">
+        <v>2311128.9182004202</v>
+      </c>
+      <c r="H66" s="17">
+        <v>12104588.490715969</v>
+      </c>
+      <c r="I66" s="17">
+        <v>9376392.18772012</v>
+      </c>
+      <c r="J66" s="17">
+        <v>14891650.637779195</v>
+      </c>
+      <c r="K66" s="17">
+        <v>5515258.4500590749</v>
+      </c>
+      <c r="L66" s="16">
+        <v>2787062.1470632264</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel4.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel4.xlsx
@@ -402,7 +402,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -594,6 +594,9 @@
                 </c:pt>
                 <c:pt idx="63">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -603,7 +606,7 @@
               <c:f>'model4(1)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -794,6 +797,9 @@
                   <c:v>9376392.18772012</c:v>
                 </c:pt>
                 <c:pt idx="63">
+                  <c:v>9376392.18772012</c:v>
+                </c:pt>
+                <c:pt idx="64">
                   <c:v>9376392.18772012</c:v>
                 </c:pt>
               </c:numCache>
@@ -837,7 +843,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1029,6 +1035,9 @@
                 </c:pt>
                 <c:pt idx="63">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1038,7 +1047,7 @@
               <c:f>'model4(1)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1230,6 +1239,9 @@
                 </c:pt>
                 <c:pt idx="63">
                   <c:v>14891650.637779195</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>14989831.863008782</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1272,7 +1284,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1464,6 +1476,9 @@
                 </c:pt>
                 <c:pt idx="63">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1473,7 +1488,7 @@
               <c:f>'model4(1)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1665,6 +1680,9 @@
                 </c:pt>
                 <c:pt idx="63">
                   <c:v>5515258.4500590749</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>5613439.6752886623</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1686,11 +1704,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="77073408"/>
-        <c:axId val="508912384"/>
+        <c:axId val="86720512"/>
+        <c:axId val="86723968"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="77073408"/>
+        <c:axId val="86720512"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1733,14 +1751,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="508912384"/>
+        <c:crossAx val="86723968"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="508912384"/>
+        <c:axId val="86723968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1791,7 +1809,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="77073408"/>
+        <c:crossAx val="86720512"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1952,7 +1970,7 @@
               <c:f>'model4(1)'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2144,6 +2162,9 @@
                 </c:pt>
                 <c:pt idx="63">
                   <c:v>-314574.39222416701</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>-309173.41467680095</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2158,8 +2179,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="676456704"/>
-        <c:axId val="676454784"/>
+        <c:axId val="485508224"/>
+        <c:axId val="428227968"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2184,7 +2205,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -2376,6 +2397,9 @@
                 </c:pt>
                 <c:pt idx="63">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2385,7 +2409,7 @@
               <c:f>'model4(1)'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>4.7860299999999993</c:v>
                 </c:pt>
@@ -2577,6 +2601,9 @@
                 </c:pt>
                 <c:pt idx="63">
                   <c:v>5.2375219726562499</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>5.2800039062500002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2593,11 +2620,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="547349248"/>
-        <c:axId val="547351168"/>
+        <c:axId val="427129472"/>
+        <c:axId val="428226432"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="547349248"/>
+        <c:axId val="427129472"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2640,14 +2667,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="547351168"/>
+        <c:crossAx val="428226432"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="547351168"/>
+        <c:axId val="428226432"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2698,12 +2725,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="547349248"/>
+        <c:crossAx val="427129472"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="676454784"/>
+        <c:axId val="428227968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2740,12 +2767,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="676456704"/>
+        <c:crossAx val="485508224"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="676456704"/>
+        <c:axId val="485508224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2754,7 +2781,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="676454784"/>
+        <c:crossAx val="428227968"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3163,7 +3190,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG66"/>
+  <dimension ref="A1:AG67"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -5943,6 +5970,44 @@
         <v>2787062.1470632264</v>
       </c>
     </row>
+    <row r="67" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A67" s="14">
+        <v>46265</v>
+      </c>
+      <c r="B67" s="15">
+        <v>5.2800039062500002</v>
+      </c>
+      <c r="C67" s="15">
+        <v>35.77999878</v>
+      </c>
+      <c r="D67" s="16">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E67" s="16">
+        <v>-309173.41467680095</v>
+      </c>
+      <c r="F67" s="17">
+        <v>-58555.527640960434</v>
+      </c>
+      <c r="G67" s="17">
+        <v>2252573.3905594596</v>
+      </c>
+      <c r="H67" s="17">
+        <v>11893596.301268755</v>
+      </c>
+      <c r="I67" s="17">
+        <v>9376392.18772012</v>
+      </c>
+      <c r="J67" s="17">
+        <v>14989831.863008782</v>
+      </c>
+      <c r="K67" s="17">
+        <v>5613439.6752886623</v>
+      </c>
+      <c r="L67" s="16">
+        <v>3096235.5617400273</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">
